--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104689_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104689_W26.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7272</v>
+        <v>3.7267</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2143</v>
+        <v>3.0868</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5128</v>
+        <v>0.64</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8285</v>
+        <v>4.8383</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7098</v>
+        <v>1.7144</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1187</v>
+        <v>3.124</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6965</v>
+        <v>4.6797</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7187</v>
+        <v>2.7062</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="M2" t="n">
-        <v>0.132</v>
+        <v>0.1586</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3548</v>
+        <v>-0.3589</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1769</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2731</v>
+        <v>-0.1819</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.715</v>
+        <v>2.3428</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8019</v>
+        <v>6.2104</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.0869</v>
+        <v>-3.8676</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4593</v>
+        <v>2.4274</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4675</v>
+        <v>2.4644</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.037</v>
       </c>
       <c r="J3" t="n">
-        <v>5.289</v>
+        <v>5.2349</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2555</v>
+        <v>3.2405</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0335</v>
+        <v>1.9943</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8298</v>
+        <v>-2.8075</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3568</v>
+        <v>-0.6992</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8184</v>
+        <v>-0.6339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5835</v>
+        <v>2.1319</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1206</v>
+        <v>1.4549</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4629</v>
+        <v>0.677</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6903</v>
+        <v>1.6812</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2843</v>
+        <v>-1.2811</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9746</v>
+        <v>2.9623</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1874</v>
+        <v>2.1543</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3055</v>
+        <v>2.2857</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4971</v>
+        <v>-0.4731</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1995</v>
+        <v>-0.6388</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0253</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1742</v>
+        <v>0.0119</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0321</v>
+        <v>1.1757</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8393</v>
+        <v>1.9445</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8072</v>
+        <v>-0.7687</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5295</v>
+        <v>2.5287</v>
       </c>
       <c r="H5" t="n">
         <v>0.2958</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2337</v>
+        <v>2.2329</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1822</v>
+        <v>3.1733</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L5" t="n">
-        <v>2.351</v>
+        <v>2.3459</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6526</v>
+        <v>-0.6446</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5901</v>
+        <v>-0.4425</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3814</v>
+        <v>-0.3518</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7827</v>
+        <v>0.6118</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9382</v>
+        <v>1.6847</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1555</v>
+        <v>-1.0729</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8432</v>
+        <v>-1.8391</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5238</v>
+        <v>-0.5255</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3194</v>
+        <v>-1.3136</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3379</v>
+        <v>-0.3499</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4125</v>
+        <v>-0.4244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5053</v>
+        <v>-1.4891</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.2532</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.17</v>
+        <v>-0.1089</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1725</v>
+        <v>0.015</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1294</v>
+        <v>-1.4962</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3019</v>
+        <v>1.5112</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8302</v>
+        <v>0.8239</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2813</v>
+        <v>-0.2842</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1115</v>
+        <v>1.1081</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6455</v>
+        <v>0.6208</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1701</v>
+        <v>-0.1831</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1847</v>
+        <v>0.2032</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.274</v>
+        <v>-0.4204</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0302</v>
+        <v>-0.3627</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2438</v>
+        <v>-0.0578</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-1.074</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0552</v>
+        <v>-1.8199</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3329</v>
+        <v>0.7459</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5356</v>
+        <v>-0.533</v>
       </c>
       <c r="H8" t="n">
-        <v>0.264</v>
+        <v>0.2669</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7997</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1872</v>
+        <v>-1.2087</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0979</v>
+        <v>-2.1083</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6515</v>
+        <v>0.6757</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3448</v>
+        <v>-0.0253</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.868</v>
+        <v>-0.6112</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2128</v>
+        <v>0.5859</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5383</v>
+        <v>-1.7198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8448</v>
+        <v>-1.5615</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3831</v>
+        <v>-0.1583</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2759</v>
+        <v>-1.7048</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2008</v>
+        <v>-0.1588</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4767</v>
+        <v>-1.546</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0092</v>
+        <v>0.1275</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1385</v>
+        <v>0.1724</v>
       </c>
       <c r="L9" t="n">
-        <v>2.8707</v>
+        <v>-0.0449</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7334</v>
+        <v>-1.8323</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3393</v>
+        <v>-0.3312</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.394</v>
+        <v>-1.5011</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8003</v>
+        <v>-0.015</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1039</v>
+        <v>-0.5508</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3037</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6944</v>
+        <v>-2.3026</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9749</v>
+        <v>1.2388</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2805</v>
+        <v>-3.5414</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7261</v>
+        <v>0.2873</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1749</v>
+        <v>-1.1842</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5513</v>
+        <v>1.4715</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1331</v>
+        <v>2.9975</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1732</v>
+        <v>0.1379</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.04</v>
+        <v>2.8596</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8593</v>
+        <v>-2.7102</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.348</v>
+        <v>-1.3221</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5113</v>
+        <v>-1.3881</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0317</v>
+        <v>0.0232</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9739</v>
+        <v>0.5177</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0056</v>
+        <v>-0.4945</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4936</v>
+        <v>-4.4676</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1517</v>
+        <v>-3.8298</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3419</v>
+        <v>-0.6378</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2627</v>
+        <v>-3.2679</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1789</v>
+        <v>-1.3445</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4416</v>
+        <v>-1.9234</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6051</v>
+        <v>-3.6554</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0693</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6744</v>
+        <v>-2.9724</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6576</v>
+        <v>0.3875</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1096</v>
+        <v>-0.6615</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7672</v>
+        <v>1.049</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4162</v>
+        <v>-0.7444</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2782</v>
+        <v>-0.1258</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1379</v>
+        <v>-0.6187</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6407</v>
+        <v>-4.5009</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6333</v>
+        <v>-3.0457</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0074</v>
+        <v>-1.4552</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2673</v>
+        <v>-2.2548</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3507</v>
+        <v>0.1836</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9166</v>
+        <v>-2.4384</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6311</v>
+        <v>-0.609</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6722</v>
+        <v>0.0689</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.9588</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3638</v>
+        <v>-1.6458</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6785</v>
+        <v>0.1146</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0423</v>
+        <v>-1.7604</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9197</v>
+        <v>-0.425</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0393</v>
+        <v>-0.1604</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9591</v>
+        <v>-0.2647</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2053</v>
+        <v>-5.5355</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5271</v>
+        <v>-4.1981</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6782</v>
+        <v>-1.3375</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.2284</v>
+        <v>-4.2243</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6566</v>
+        <v>-0.6522</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.5718</v>
+        <v>-3.5721</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.7155</v>
+        <v>-2.7368</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0605</v>
+        <v>-2.071</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.513</v>
+        <v>-1.4876</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6574</v>
+        <v>-0.9941</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6775</v>
+        <v>-0.3232</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9799</v>
+        <v>-0.671</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.2816</v>
+        <v>-9.596500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7125000000000012</v>
+        <v>-0.3311000000000011</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.5692</v>
+        <v>-9.2653</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.249600000000001</v>
+        <v>-1.2371</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5564000000000006</v>
+        <v>-0.5053999999999997</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6934000000000009</v>
+        <v>-0.7316000000000007</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6661</v>
+        <v>10.4282</v>
       </c>
       <c r="K14" t="n">
-        <v>6.069299999999998</v>
+        <v>5.9653</v>
       </c>
       <c r="L14" t="n">
-        <v>4.5971</v>
+        <v>4.462999999999997</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.9161</v>
+        <v>-11.6652</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.625699999999999</v>
+        <v>-6.4706</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.2903</v>
+        <v>-5.1946</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.2684</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.6709</v>
+        <v>-4.993599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.4478</v>
+        <v>-2.7443</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2231</v>
+        <v>-2.2496</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0893</v>
       </c>
       <c r="W14" t="n">
-        <v>6.813299999999999</v>
+        <v>6.7809</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.905999999999999</v>
+        <v>-7.8704</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.741</v>
+        <v>9.127800000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.073700000000001</v>
+        <v>8.24</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6673</v>
+        <v>0.8878</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7314</v>
+        <v>4.6996</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8741</v>
+        <v>-0.8949</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6055</v>
+        <v>5.5945</v>
       </c>
       <c r="J15" t="n">
-        <v>5.458</v>
+        <v>5.3975</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2433</v>
+        <v>-0.2768</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7013</v>
+        <v>5.6742</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7266</v>
+        <v>-0.6979</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1418</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1089</v>
+        <v>0.348</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0329</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.776</v>
+        <v>3.5139</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1451</v>
+        <v>2.8782</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6308</v>
+        <v>0.6357</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2425</v>
+        <v>1.2676</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7705</v>
+        <v>1.4628</v>
       </c>
       <c r="I16" t="n">
-        <v>1.013</v>
+        <v>-0.1952</v>
       </c>
       <c r="J16" t="n">
-        <v>1.465</v>
+        <v>3.1131</v>
       </c>
       <c r="K16" t="n">
-        <v>0.159</v>
+        <v>2.5403</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3061</v>
+        <v>0.5728</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2225</v>
+        <v>-1.8455</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9294</v>
+        <v>-1.0775</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2931</v>
+        <v>-0.768</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0117</v>
+        <v>0.4041</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5194</v>
+        <v>-0.1862</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4924</v>
+        <v>0.5903</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1607</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9613</v>
+        <v>3.1185</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9259</v>
+        <v>2.2416</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0353</v>
+        <v>0.877</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2847</v>
+        <v>0.2455</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4793</v>
+        <v>-0.7752</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1946</v>
+        <v>1.0207</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1549</v>
+        <v>1.4477</v>
       </c>
       <c r="K17" t="n">
-        <v>2.566</v>
+        <v>0.1444</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5889</v>
+        <v>1.3033</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8702</v>
+        <v>-1.2022</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0867</v>
+        <v>-0.9196</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7835</v>
+        <v>-0.2826</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1627</v>
+        <v>1.3495</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1875</v>
+        <v>0.6361</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0248</v>
+        <v>0.7134</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8455</v>
+        <v>2.9058</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2184</v>
+        <v>0.4324</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6271</v>
+        <v>2.4734</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7136</v>
+        <v>1.7248</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0894</v>
+        <v>2.0908</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3758</v>
+        <v>-0.366</v>
       </c>
       <c r="J18" t="n">
-        <v>2.078</v>
+        <v>2.0635</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0434</v>
+        <v>2.0339</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3644</v>
+        <v>-0.3387</v>
       </c>
       <c r="N18" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>1.198</v>
+        <v>1.2509</v>
       </c>
       <c r="T18" t="n">
-        <v>0.248</v>
+        <v>0.4874</v>
       </c>
       <c r="U18" t="n">
-        <v>0.95</v>
+        <v>0.7634</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.021</v>
+        <v>2.1303</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8138</v>
+        <v>0.9339</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2072</v>
+        <v>1.1964</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5417</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.218</v>
+        <v>-0.2101</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7598</v>
+        <v>0.7691</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3571</v>
+        <v>0.3558</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2078</v>
+        <v>0.2068</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1847</v>
+        <v>0.2032</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5719</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4567</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1152</v>
+        <v>0.0827</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5612</v>
+        <v>0.1636</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6851</v>
+        <v>1.0691</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1239</v>
+        <v>-0.9054</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0804</v>
+        <v>-1.085</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1368</v>
+        <v>-0.1514</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9435</v>
+        <v>-0.9335</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3028</v>
+        <v>-0.329</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4462</v>
+        <v>0.4234</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7776</v>
+        <v>-0.756</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8949</v>
+        <v>0.4958</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8953</v>
+        <v>0.3085</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0003</v>
+        <v>0.1873</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2046</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>3.0299</v>
+        <v>2.7895</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8253</v>
+        <v>-2.7141</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2495</v>
+        <v>2.2487</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8528</v>
+        <v>0.853</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3967</v>
+        <v>1.3957</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3827</v>
+        <v>2.3762</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8285</v>
+        <v>1.8246</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1331</v>
+        <v>-0.1275</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5526</v>
+        <v>0.4122</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6472</v>
+        <v>0.4133</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2046</v>
+        <v>-0.0189</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7258</v>
+        <v>0.1949</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9304</v>
+        <v>-0.2138</v>
       </c>
       <c r="G22" t="n">
-        <v>0.504</v>
+        <v>-0.4695</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2771</v>
+        <v>-0.1523</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7811</v>
+        <v>-0.3172</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3802</v>
+        <v>0.1462</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1487</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2315</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8762</v>
+        <v>-0.6157</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4258</v>
+        <v>-0.1868</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4504</v>
+        <v>-0.4289</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6109</v>
+        <v>-0.0046</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3871</v>
+        <v>0.0487</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2238</v>
+        <v>-0.0534</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2057</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.077</v>
+        <v>1.8297</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2827</v>
+        <v>-1.9026</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4743</v>
+        <v>0.5125</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1544</v>
+        <v>-0.2758</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3198</v>
+        <v>0.7883</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1466</v>
+        <v>1.37</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0346</v>
+        <v>0.1411</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112</v>
+        <v>1.2288</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6209</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1891</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4318</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1851</v>
+        <v>0.7316</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0696</v>
+        <v>0.5084</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1155</v>
+        <v>0.2232</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9542</v>
+        <v>-1.0245</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0836</v>
+        <v>-2.4029</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1295</v>
+        <v>1.3784</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3154</v>
+        <v>-3.3148</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8471</v>
+        <v>-0.8418</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.4683</v>
+        <v>-2.473</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2074</v>
+        <v>-2.2285</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4054</v>
+        <v>-0.4104</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.802</v>
+        <v>-1.818</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.108</v>
+        <v>-1.0863</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1851</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8347</v>
+        <v>-0.1258</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6496</v>
+        <v>0.8713</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1559</v>
+        <v>-3.5107</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1693</v>
+        <v>-2.6142</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9866</v>
+        <v>-0.8965</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.0605</v>
+        <v>-3.0668</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0907</v>
+        <v>-1.1022</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9698</v>
+        <v>-1.9646</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2916</v>
+        <v>-1.3199</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1692</v>
+        <v>0.1477</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7689</v>
+        <v>-1.7469</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.483</v>
+        <v>0.1707</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9043</v>
+        <v>-0.3139</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4213</v>
+        <v>0.4846</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.3086</v>
+        <v>-4.5356</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.8726</v>
+        <v>-6.3267</v>
       </c>
       <c r="F26" t="n">
-        <v>1.564</v>
+        <v>1.7911</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0873</v>
+        <v>-2.0846</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5036</v>
+        <v>0.5027</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.5909</v>
+        <v>-2.5873</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7047</v>
+        <v>-0.7274</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.3825</v>
+        <v>-1.3573</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2952</v>
+        <v>0.4855</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0434</v>
+        <v>-0.4533</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7482</v>
+        <v>0.9388</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1568</v>
+        <v>1.1609</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>10.2816</v>
+        <v>11.8727</v>
       </c>
       <c r="E27" t="n">
-        <v>9.5692</v>
+        <v>9.265499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7123</v>
+        <v>2.6074</v>
       </c>
       <c r="G27" t="n">
-        <v>1.249499999999999</v>
+        <v>1.236999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5563999999999996</v>
+        <v>0.5056000000000006</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6933999999999991</v>
+        <v>0.7315000000000014</v>
       </c>
       <c r="J27" t="n">
-        <v>11.916</v>
+        <v>11.6652</v>
       </c>
       <c r="K27" t="n">
-        <v>6.6256</v>
+        <v>6.470499999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>5.290300000000001</v>
+        <v>5.194500000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.6662</v>
+        <v>-10.4282</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.0694</v>
+        <v>-5.9653</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.5969</v>
+        <v>-4.463</v>
       </c>
       <c r="P27" t="n">
-        <v>2.268399999999999</v>
+        <v>2.2764</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R27" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S27" t="n">
-        <v>5.670699999999999</v>
+        <v>7.27</v>
       </c>
       <c r="T27" t="n">
-        <v>2.223100000000001</v>
+        <v>2.2493</v>
       </c>
       <c r="U27" t="n">
-        <v>3.4477</v>
+        <v>5.020499999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>1.0927</v>
+        <v>1.089499999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>7.906000000000001</v>
+        <v>7.8706</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.8132</v>
+        <v>-6.780799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104689_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104689_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.8704</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104689_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.780799999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
